--- a/daily logs.xlsx
+++ b/daily logs.xlsx
@@ -14,17 +14,17 @@
   <calcPr iterateDelta="0.0001"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1788686237" val="1234" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1788686237" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1788686237" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1788686237"/>
+      <pm:revision xmlns:pm="smNativeData" day="1788866525" val="1234" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1788866525" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1788866525" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1788866525"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,6 +205,9 @@
   <si>
     <t>Low</t>
   </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -231,7 +234,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -246,7 +249,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -262,7 +265,7 @@
       <sz val="18"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="1F4E78" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="1F4E78" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="360" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="360" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="360" lang="default" weight="bold"/>
@@ -278,7 +281,7 @@
       <sz val="13"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="595959" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="595959" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="260" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="260" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="260" lang="default" weight="bold"/>
@@ -294,7 +297,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="595959" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="595959" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" i="1"/>
             <pm:cs face="Basic Roman" sz="200" lang="default" i="1"/>
             <pm:ea face="Basic Roman" sz="200" lang="default" i="1"/>
@@ -309,7 +312,7 @@
       <sz val="10.50"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="210" lang="default"/>
             <pm:cs face="Basic Roman" sz="210" lang="default"/>
             <pm:ea face="Basic Roman" sz="210" lang="default"/>
@@ -325,7 +328,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="1F4E78" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="1F4E78" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -341,7 +344,7 @@
       <sz val="13"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="1F4E78" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="1F4E78" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="260" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="260" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="260" lang="default" weight="bold"/>
@@ -357,7 +360,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -373,7 +376,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="595959" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="595959" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="180" lang="default" i="1"/>
             <pm:cs face="Basic Roman" sz="180" lang="default" i="1"/>
             <pm:ea face="Basic Roman" sz="180" lang="default" i="1"/>
@@ -389,7 +392,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -405,7 +408,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="808080" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="808080" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default" i="1"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" i="1"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" i="1"/>
@@ -420,7 +423,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -435,7 +438,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="333333" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="333333" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -450,7 +453,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="333333" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="333333" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -472,7 +475,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788686237" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -483,7 +486,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788686237" type="1" fgLvl="100" fgClr="001F4E78" bgLvl="0" bgClr="00003366"/>
+            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="001F4E78" bgLvl="0" bgClr="00003366"/>
           </ext>
         </extLst>
       </patternFill>
@@ -497,7 +500,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788686237" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -508,7 +511,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788686237" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -519,7 +522,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788686237" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -530,7 +533,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788686237" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -552,7 +555,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788686237"/>
+          <pm:border xmlns:pm="smNativeData" id="1788866525"/>
         </ext>
       </extLst>
     </border>
@@ -571,7 +574,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788686237">
+          <pm:border xmlns:pm="smNativeData" id="1788866525">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
@@ -595,7 +598,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788686237">
+          <pm:border xmlns:pm="smNativeData" id="1788866525">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
@@ -619,7 +622,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788686237">
+          <pm:border xmlns:pm="smNativeData" id="1788866525">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
@@ -643,7 +646,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788686237">
+          <pm:border xmlns:pm="smNativeData" id="1788866525">
             <pm:line position="top" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
             <pm:line position="bottom" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
             <pm:line position="left" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
@@ -667,7 +670,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788686237">
+          <pm:border xmlns:pm="smNativeData" id="1788866525">
             <pm:line position="top" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
             <pm:line position="bottom" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
             <pm:line position="left" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
@@ -691,7 +694,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788686237"/>
+          <pm:border xmlns:pm="smNativeData" id="1788866525"/>
         </ext>
       </extLst>
     </border>
@@ -710,7 +713,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788686237"/>
+          <pm:border xmlns:pm="smNativeData" id="1788866525"/>
         </ext>
       </extLst>
     </border>
@@ -783,7 +786,7 @@
         <color rgb="FF9C0006"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1788686237" fgClr="9C0006">
+            <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="9C0006">
               <pm:latin face="Arial"/>
               <pm:cs face="Arial"/>
               <pm:ea face="Arial"/>
@@ -796,7 +799,7 @@
           <bgColor rgb="FFFFC7CE"/>
           <extLst>
             <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1788686237" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="100" bgClr="FFFFFFFF"/>
+              <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="100" bgClr="FFFFFFFF"/>
             </ext>
           </extLst>
         </patternFill>
@@ -806,10 +809,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1788686237" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1788866525" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1788686237" count="8">
+      <pm:colors xmlns:pm="smNativeData" id="1788866525" count="8">
         <pm:color name="Color 24" rgb="1F4E78"/>
         <pm:color name="Color 25" rgb="595959"/>
         <pm:color name="Color 26" rgb="808080"/>
@@ -1267,7 +1270,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1788686237" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1788866525" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -1276,14 +1279,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1788686237" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1788686237" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1788866525" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1788866525" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1788686237" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1788866525" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2065,47 +2068,91 @@
       <c r="N20" s="20"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="16"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="18" t="str">
+      <c r="A21" s="16" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="I21" s="18">
         <f>IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
-        <v/>
-      </c>
-      <c r="J21" s="18" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J21" s="18">
         <f>IF(I21="","",1440-I21)</f>
-        <v/>
-      </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
+        <v>420</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>59</v>
+      </c>
       <c r="N21" s="20"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="16"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="18" t="str">
+      <c r="A22" s="16" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="I22" s="18">
         <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="18" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J22" s="18">
         <f>IF(I22="","",1440-I22)</f>
-        <v/>
-      </c>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
+        <v>250</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>57</v>
+      </c>
       <c r="N22" s="20"/>
     </row>
     <row r="23" spans="1:14">
@@ -10481,7 +10528,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1788686237" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1788866525" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10490,14 +10537,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1788686237" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1788686237" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1788866525" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1788866525" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1788686237" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1788866525" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/daily logs.xlsx
+++ b/daily logs.xlsx
@@ -14,17 +14,17 @@
   <calcPr iterateDelta="0.0001"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1788866525" val="1234" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1788866525" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1788866525" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1788866525"/>
+      <pm:revision xmlns:pm="smNativeData" day="1789055025" val="1234" rev="124" rev64="64" revOS="1" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1789055025" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1789055025" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1789055025"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,6 +208,9 @@
   <si>
     <t>Unsatisfied</t>
   </si>
+  <si>
+    <t>202-09-10</t>
+  </si>
 </sst>
 </file>
 
@@ -234,7 +237,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -249,7 +252,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" ulstyle="none" kern="1">
             <pm:latin face="Basic Sans" sz="200" lang="default"/>
             <pm:cs face="Basic Roman" sz="200" lang="default"/>
             <pm:ea face="Basic Roman" sz="200" lang="default"/>
@@ -265,7 +268,7 @@
       <sz val="18"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="1F4E78" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="1F4E78" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="360" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="360" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="360" lang="default" weight="bold"/>
@@ -281,7 +284,7 @@
       <sz val="13"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="595959" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="595959" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="260" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="260" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="260" lang="default" weight="bold"/>
@@ -297,7 +300,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="595959" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="595959" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default" i="1"/>
             <pm:cs face="Basic Roman" sz="200" lang="default" i="1"/>
             <pm:ea face="Basic Roman" sz="200" lang="default" i="1"/>
@@ -312,7 +315,7 @@
       <sz val="10.50"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="210" lang="default"/>
             <pm:cs face="Basic Roman" sz="210" lang="default"/>
             <pm:ea face="Basic Roman" sz="210" lang="default"/>
@@ -328,7 +331,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="1F4E78" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="1F4E78" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -344,7 +347,7 @@
       <sz val="13"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="1F4E78" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="1F4E78" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="260" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="260" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="260" lang="default" weight="bold"/>
@@ -360,7 +363,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -376,7 +379,7 @@
       <sz val="9"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="595959" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="595959" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="180" lang="default" i="1"/>
             <pm:cs face="Basic Roman" sz="180" lang="default" i="1"/>
             <pm:ea face="Basic Roman" sz="180" lang="default" i="1"/>
@@ -392,7 +395,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="FFFFFF" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="FFFFFF" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default" weight="bold"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" weight="bold"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" weight="bold"/>
@@ -408,7 +411,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="808080" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="808080" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default" i="1"/>
             <pm:cs face="Basic Roman" sz="220" lang="default" i="1"/>
             <pm:ea face="Basic Roman" sz="220" lang="default" i="1"/>
@@ -423,7 +426,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -438,7 +441,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="333333" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="333333" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -453,7 +456,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="333333" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="333333" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="220" lang="default"/>
             <pm:cs face="Basic Roman" sz="220" lang="default"/>
             <pm:ea face="Basic Roman" sz="220" lang="default"/>
@@ -462,7 +465,7 @@
       </extLst>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,7 +478,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -486,7 +489,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="001F4E78" bgLvl="0" bgClr="00003366"/>
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="100" fgClr="001F4E78" bgLvl="0" bgClr="00003366"/>
           </ext>
         </extLst>
       </patternFill>
@@ -500,7 +503,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -511,7 +514,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -522,7 +525,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -533,13 +536,57 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="0" fgClr="00000000" bgLvl="100" bgClr="001F4E78"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0E0"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="12" fgClr="007F7F00" bgLvl="88" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFE0"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="100" fgClr="00FFF2CC" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -555,7 +602,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788866525"/>
+          <pm:border xmlns:pm="smNativeData" id="1789055025"/>
         </ext>
       </extLst>
     </border>
@@ -574,7 +621,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788866525">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
@@ -598,7 +645,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788866525">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
@@ -622,7 +669,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788866525">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
             <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
             <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B7B7B7"/>
@@ -646,7 +693,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788866525">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
             <pm:line position="top" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
             <pm:line position="bottom" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
             <pm:line position="left" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
@@ -670,7 +717,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788866525">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
             <pm:line position="top" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
             <pm:line position="bottom" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
             <pm:line position="left" type="1" style="0" width="15" dist="20" width2="20" rgb="595959"/>
@@ -694,7 +741,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788866525"/>
+          <pm:border xmlns:pm="smNativeData" id="1789055025"/>
         </ext>
       </extLst>
     </border>
@@ -713,7 +760,103 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1788866525"/>
+          <pm:border xmlns:pm="smNativeData" id="1789055025"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF595959"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF595959"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF595959"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF595959"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1789055025">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="595959"/>
+          </pm:border>
         </ext>
       </extLst>
     </border>
@@ -786,7 +929,7 @@
         <color rgb="FF9C0006"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:charSpec xmlns:pm="smNativeData" id="1788866525" fgClr="9C0006">
+            <pm:charSpec xmlns:pm="smNativeData" id="1789055025" fgClr="9C0006">
               <pm:latin face="Arial"/>
               <pm:cs face="Arial"/>
               <pm:ea face="Arial"/>
@@ -799,7 +942,7 @@
           <bgColor rgb="FFFFC7CE"/>
           <extLst>
             <ext uri="smNativeData">
-              <pm:shade xmlns:pm="smNativeData" id="1788866525" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="100" bgClr="FFFFFFFF"/>
+              <pm:shade xmlns:pm="smNativeData" id="1789055025" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="100" bgClr="FFFFFFFF"/>
             </ext>
           </extLst>
         </patternFill>
@@ -809,10 +952,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1788866525" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1789055025" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1788866525" count="8">
+      <pm:colors xmlns:pm="smNativeData" id="1789055025" count="8">
         <pm:color name="Color 24" rgb="1F4E78"/>
         <pm:color name="Color 25" rgb="595959"/>
         <pm:color name="Color 26" rgb="808080"/>
@@ -1270,7 +1413,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1788866525" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1789055025" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -1279,14 +1422,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1788866525" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1788866525" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1789055025" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1789055025" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1788866525" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1789055025" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2156,47 +2299,91 @@
       <c r="N22" s="20"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="16"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="18" t="str">
+      <c r="A23" s="16" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="18">
         <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
-        <v/>
-      </c>
-      <c r="J23" s="18" t="str">
+        <v>820</v>
+      </c>
+      <c r="J23" s="18">
         <f>IF(I23="","",1440-I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
+        <v>620</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>55</v>
+      </c>
       <c r="N23" s="20"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="16"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="18" t="str">
+      <c r="A24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>420</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>200</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="I24" s="18">
         <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
-        <v/>
-      </c>
-      <c r="J24" s="18" t="str">
+        <v>960</v>
+      </c>
+      <c r="J24" s="18">
         <f>IF(I24="","",1440-I24)</f>
-        <v/>
-      </c>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
+        <v>480</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>57</v>
+      </c>
       <c r="N24" s="20"/>
     </row>
     <row r="25" spans="1:14">
@@ -10528,7 +10715,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1788866525" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1789055025" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -10537,14 +10724,14 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1788866525" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1788866525" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:header xmlns:pm="smNativeData" id="1789055025" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1789055025" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1788866525" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1789055025" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
